--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Февраль 2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Февраль 2025/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92557053594</v>
+        <v>46157.93118864435</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Февраль 2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Февраль 2025/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93118864435</v>
+        <v>46157.93140564759</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Февраль 2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Февраль 2025/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93140564759</v>
+        <v>46157.93387117221</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Февраль 2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Февраль 2025/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93387117221</v>
+        <v>46157.9369901859</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Февраль 2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Февраль 2025/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9369901859</v>
+        <v>46158.28206528148</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Февраль 2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Февраль 2025/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28206528148</v>
+        <v>46158.29655982473</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Февраль 2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Февраль 2025/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29655982473</v>
+        <v>46158.29795790616</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Февраль 2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Февраль 2025/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29795790616</v>
+        <v>46158.33373203492</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Февраль 2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Февраль 2025/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33373203492</v>
+        <v>46158.37226788804</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Февраль 2025/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Февраль 2025/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37226788804</v>
+        <v>46158.37277169493</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
